--- a/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -953,7 +953,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.666667</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4261,10 +4261,10 @@
         <v>0.975652</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0.977414</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J167" t="n">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J203" t="n">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -9467,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2</v>
+        <v>0.285714</v>
       </c>
       <c r="J210" t="n">
         <v>1</v>
@@ -9596,7 +9596,7 @@
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J213" t="n">
         <v>1</v>
@@ -9639,7 +9639,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -9811,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4</v>
+        <v>0.285714</v>
       </c>
       <c r="J218" t="n">
         <v>1</v>
@@ -9854,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J219" t="n">
         <v>1</v>
@@ -9940,7 +9940,7 @@
         <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J221" t="n">
         <v>1</v>
@@ -10026,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2</v>
+        <v>0.285714</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -10112,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="I225" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J225" t="n">
         <v>1</v>
@@ -10284,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -10370,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="I231" t="n">
-        <v>0.2</v>
+        <v>0.285714</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2</v>
+        <v>0.285714</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -10499,7 +10499,7 @@
         <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -10542,7 +10542,7 @@
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -10585,7 +10585,7 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>0.4</v>
+        <v>0.428571</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -10671,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J238" t="n">
         <v>1</v>
@@ -10972,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J245" t="n">
         <v>1</v>
@@ -11015,7 +11015,7 @@
         <v>1</v>
       </c>
       <c r="I246" t="n">
-        <v>0.6</v>
+        <v>0.857143</v>
       </c>
       <c r="J246" t="n">
         <v>1</v>
@@ -11058,7 +11058,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -11144,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4</v>
+        <v>0.285714</v>
       </c>
       <c r="J249" t="n">
         <v>1</v>
@@ -11187,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J252" t="n">
         <v>1</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
         <v>1</v>
       </c>
       <c r="I256" t="n">
-        <v>0.6</v>
+        <v>0.571429</v>
       </c>
       <c r="J256" t="n">
         <v>1</v>
@@ -11488,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4</v>
+        <v>0.285714</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -11531,7 +11531,7 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6</v>
+        <v>0.714286</v>
       </c>
       <c r="J258" t="n">
         <v>1</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4</v>
+        <v>0.428571</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -11617,7 +11617,7 @@
         <v>0</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -11660,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -11703,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -11789,7 +11789,7 @@
         <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
@@ -11832,7 +11832,7 @@
         <v>0</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -11961,7 +11961,7 @@
         <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -12262,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -12735,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>0.4</v>
+        <v>0.285714</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -12821,7 +12821,7 @@
         <v>0</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="I289" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -12907,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="I290" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -12993,7 +12993,7 @@
         <v>0</v>
       </c>
       <c r="I292" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -13036,7 +13036,7 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -13079,7 +13079,7 @@
         <v>0</v>
       </c>
       <c r="I294" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -13165,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
-        <v>0.2</v>
+        <v>0.285714</v>
       </c>
       <c r="J296" t="n">
         <v>1</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2</v>
+        <v>0.285714</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -13423,7 +13423,7 @@
         <v>0</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2</v>
+        <v>0.428571</v>
       </c>
       <c r="J302" t="n">
         <v>0</v>
@@ -13466,7 +13466,7 @@
         <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6</v>
+        <v>0.714286</v>
       </c>
       <c r="J303" t="n">
         <v>1</v>
@@ -13506,10 +13506,10 @@
         <v>0.864213</v>
       </c>
       <c r="H304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4</v>
+        <v>0.571429</v>
       </c>
       <c r="J304" t="n">
         <v>1</v>
@@ -13552,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="I305" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J305" t="n">
         <v>0</v>
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>0.4</v>
+        <v>0.428571</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
@@ -13638,7 +13638,7 @@
         <v>0</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4</v>
+        <v>0.428571</v>
       </c>
       <c r="J307" t="n">
         <v>1</v>
@@ -13724,7 +13724,7 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>0.6</v>
+        <v>0.571429</v>
       </c>
       <c r="J309" t="n">
         <v>1</v>
@@ -13767,7 +13767,7 @@
         <v>0</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2</v>
+        <v>0.142857</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -13853,7 +13853,7 @@
         <v>0</v>
       </c>
       <c r="I312" t="n">
-        <v>0</v>
+        <v>0.142857</v>
       </c>
       <c r="J312" t="n">
         <v>0</v>

--- a/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.179311</v>
+        <v>0.22406</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.30919</v>
+        <v>0.341194</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.16935</v>
+        <v>0.296105</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.977414</v>
+        <v>0.788519</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.200487</v>
+        <v>0.231757</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.878723</v>
+        <v>0.793829</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.104618</v>
+        <v>0.328634</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.192862</v>
+        <v>0.298756</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.158034</v>
+        <v>0.295003</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.16857</v>
+        <v>0.136229</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.146973</v>
+        <v>0.274294</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.239296</v>
+        <v>0.356151</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.258373</v>
+        <v>0.404669</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.099371</v>
+        <v>0.166339</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.927376</v>
+        <v>0.538455</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.13346</v>
+        <v>0.295212</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.400082</v>
+        <v>0.482207</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.993533</v>
+        <v>0.859106</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.901223</v>
+        <v>0.763177</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.241176</v>
+        <v>0.377451</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.164212</v>
+        <v>0.279467</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5846,10 +5846,10 @@
         <v>0.08444500000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.721448</v>
+        <v>0.388931</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.08784699999999999</v>
+        <v>0.248774</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.164421</v>
+        <v>0.447266</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.910463</v>
+        <v>0.565947</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.302415</v>
+        <v>0.218789</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.16044</v>
+        <v>0.184012</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.178368</v>
+        <v>0.384506</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.312103</v>
+        <v>0.40562</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.255754</v>
+        <v>0.262376</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.200836</v>
+        <v>0.209158</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.173612</v>
+        <v>0.31713</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.180463</v>
+        <v>0.282758</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.198975</v>
+        <v>0.293913</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.22926</v>
+        <v>0.349587</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.098911</v>
+        <v>0.173959</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6491,10 +6491,10 @@
         <v>0.002305</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0.171724</v>
+        <v>0.535</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.149863</v>
+        <v>0.272803</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.155287</v>
+        <v>0.173048</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6620,10 +6620,10 @@
         <v>1e-06</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.874305</v>
+        <v>0.300662</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.175153</v>
+        <v>0.252</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.180761</v>
+        <v>0.236413</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.252583</v>
+        <v>0.345364</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.172173</v>
+        <v>0.256707</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0.5164339999999999</v>
+        <v>0.596024</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.234441</v>
+        <v>0.202278</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.591954</v>
+        <v>0.539979</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.998895</v>
+        <v>0.923667</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.115295</v>
+        <v>0.273249</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.288723</v>
+        <v>0.308632</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.120064</v>
+        <v>0.347701</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.389676</v>
+        <v>0.386536</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0.749247</v>
+        <v>0.594243</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.488412</v>
+        <v>0.420899</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.130867</v>
+        <v>0.164616</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.265559</v>
+        <v>0.275158</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.248906</v>
+        <v>0.205315</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7394,10 +7394,10 @@
         <v>0.004674</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.628799</v>
+        <v>0.394034</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.61948</v>
+        <v>0.505455</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0.7690630000000001</v>
+        <v>0.6771</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.238003</v>
+        <v>0.231142</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.690605</v>
+        <v>0.810569</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.163563</v>
+        <v>0.255722</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.21427</v>
+        <v>0.322866</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.306691</v>
+        <v>0.317348</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.213352</v>
+        <v>0.34598</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.226803</v>
+        <v>0.424168</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.092345</v>
+        <v>0.313799</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.200999</v>
+        <v>0.441803</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.13172</v>
+        <v>0.208136</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.253095</v>
+        <v>0.30016</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.178193</v>
+        <v>0.165284</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.129209</v>
+        <v>0.229618</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.163537</v>
+        <v>0.206268</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.124673</v>
+        <v>0.131957</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.215279</v>
+        <v>0.347928</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.205333</v>
+        <v>0.392095</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.234528</v>
+        <v>0.256655</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.187055</v>
+        <v>0.218188</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.165946</v>
+        <v>0.230187</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.160222</v>
+        <v>0.267194</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.132584</v>
+        <v>0.28551</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.283044</v>
+        <v>0.200599</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.374519</v>
+        <v>0.440541</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.146509</v>
+        <v>0.179106</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.8306210000000001</v>
+        <v>0.677128</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8641,10 +8641,10 @@
         <v>0.004186</v>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.522995</v>
+        <v>0.493124</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.263222</v>
+        <v>0.370642</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.306991</v>
+        <v>0.318718</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.455002</v>
+        <v>0.313155</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.283087</v>
+        <v>0.351448</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.145004</v>
+        <v>0.239031</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.518301</v>
+        <v>0.564611</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.888161</v>
+        <v>0.582511</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.985425</v>
+        <v>0.878504</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.347357</v>
+        <v>0.337119</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.132261</v>
+        <v>0.232642</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.256062</v>
+        <v>0.106932</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.143811</v>
+        <v>0.114023</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.243414</v>
+        <v>0.249809</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.144682</v>
+        <v>0.132346</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0.735915</v>
+        <v>0.616278</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.192761</v>
+        <v>0.277801</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.997237</v>
+        <v>0.999926</v>
       </c>
       <c r="H320" t="n">
         <v>1</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.105229</v>
+        <v>0.032595</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.378071</v>
+        <v>0.195166</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.162088</v>
+        <v>0.08956600000000001</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14360,10 +14360,10 @@
         <v>3e-06</v>
       </c>
       <c r="F324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.514942</v>
+        <v>0.242919</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.189232</v>
+        <v>0.170725</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.306094</v>
+        <v>0.155452</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.318505</v>
+        <v>0.276643</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14532,10 +14532,10 @@
         <v>0.224436</v>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G328" t="n">
-        <v>0.624085</v>
+        <v>0.416072</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.27529</v>
+        <v>0.128449</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.218228</v>
+        <v>0.196256</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.942728</v>
+        <v>0.907926</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.165538</v>
+        <v>0.07106700000000001</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.9954769999999999</v>
+        <v>0.995455</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="G334" t="n">
-        <v>0.841015</v>
+        <v>0.674685</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.452643</v>
+        <v>0.346801</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14876,10 +14876,10 @@
         <v>0.002059</v>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.7490059999999999</v>
+        <v>0.448576</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.09683</v>
+        <v>0.054622</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.142066</v>
+        <v>0.102057</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.142539</v>
+        <v>0.08379499999999999</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.374356</v>
+        <v>0.358059</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.457942</v>
+        <v>0.398572</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.06718300000000001</v>
+        <v>0.046264</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.090224</v>
+        <v>0.044694</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.134726</v>
+        <v>0.056056</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.381367</v>
+        <v>0.125586</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.426933</v>
+        <v>0.158648</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.359617</v>
+        <v>0.138353</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.192653</v>
+        <v>0.217933</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.385491</v>
+        <v>0.355007</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.758509</v>
+        <v>0.840993</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.329137</v>
+        <v>0.290999</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.338959</v>
+        <v>0.341568</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.230515</v>
+        <v>0.153638</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.264673</v>
+        <v>0.070988</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.175035</v>
+        <v>0.149737</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.164798</v>
+        <v>0.135636</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.257157</v>
+        <v>0.177223</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15822,10 +15822,10 @@
         <v>0.390569</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.431619</v>
+        <v>0.559186</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.176264</v>
+        <v>0.073745</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>0.178626</v>
+        <v>0.205369</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.492226</v>
+        <v>0.321726</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15994,10 +15994,10 @@
         <v>0.220499</v>
       </c>
       <c r="F362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>0.517963</v>
+        <v>0.412448</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.173565</v>
+        <v>0.165438</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.597387</v>
+        <v>0.625425</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.174893</v>
+        <v>0.116181</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.179442</v>
+        <v>0.138592</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.345836</v>
+        <v>0.287426</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.380402</v>
+        <v>0.310722</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.354836</v>
+        <v>0.281922</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.349772</v>
+        <v>0.236741</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16381,10 +16381,10 @@
         <v>0.277288</v>
       </c>
       <c r="F371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0.484407</v>
+        <v>0.6059600000000001</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.25485</v>
+        <v>0.118325</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.303671</v>
+        <v>0.263372</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.367194</v>
+        <v>0.401245</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.231915</v>
+        <v>0.226082</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.296172</v>
+        <v>0.06256200000000001</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.160259</v>
+        <v>0.069398</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.265581</v>
+        <v>0.129585</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.286377</v>
+        <v>0.217863</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.932047</v>
+        <v>0.65294</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.332181</v>
+        <v>0.155239</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.290468</v>
+        <v>0.108173</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.193117</v>
+        <v>0.138739</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.223195</v>
+        <v>0.107649</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.178384</v>
+        <v>0.08995599999999999</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.147375</v>
+        <v>0.12919</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.465335</v>
+        <v>0.311033</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.230246</v>
+        <v>0.227794</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.228705</v>
+        <v>0.126867</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.25225</v>
+        <v>0.209922</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.423014</v>
+        <v>0.293297</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.406215</v>
+        <v>0.492731</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.689426</v>
+        <v>0.836924</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.30472</v>
+        <v>0.133426</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.861847</v>
+        <v>0.89016</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.31416</v>
+        <v>0.254934</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.511236</v>
+        <v>0.610472</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.397794</v>
+        <v>0.378272</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.21506</v>
+        <v>0.186773</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.305688</v>
+        <v>0.275391</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17671,10 +17671,10 @@
         <v>0.762657</v>
       </c>
       <c r="F401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.579836</v>
+        <v>0.312607</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.138819</v>
+        <v>0.210993</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.575838</v>
+        <v>0.692196</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.269616</v>
+        <v>0.134636</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.198426</v>
+        <v>0.08819399999999999</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.365508</v>
+        <v>0.122142</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17929,10 +17929,10 @@
         <v>0.010818</v>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.490967</v>
+        <v>0.504201</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.760327</v>
+        <v>0.631641</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.331359</v>
+        <v>0.453955</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.21616</v>
+        <v>0.134882</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.734647</v>
+        <v>0.5363599999999999</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.455749</v>
+        <v>0.296677</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.236131</v>
+        <v>0.130874</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.997525</v>
+        <v>0.997665</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
